--- a/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-1011_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUCILA-RUBIO-DE-LAVERDE-(IED)-1011_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3076,11 +3040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3329,11 +3289,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3578,11 +3534,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -3831,11 +3783,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4084,11 +4032,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4337,11 +4281,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4590,11 +4530,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -4843,11 +4779,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5096,11 +5028,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5349,11 +5277,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5602,11 +5526,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -5855,11 +5775,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6108,11 +6024,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6357,11 +6269,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6610,11 +6518,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -6855,11 +6759,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7108,11 +7008,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7361,11 +7257,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7614,11 +7506,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -7867,11 +7755,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8120,11 +8004,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8373,11 +8253,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8626,11 +8502,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -8879,11 +8751,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9132,11 +9000,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9385,11 +9249,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9638,11 +9498,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -9891,11 +9747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10144,11 +9996,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10397,11 +10245,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10650,11 +10494,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -10899,11 +10739,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11152,11 +10988,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11405,11 +11237,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -11911,11 +11735,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12164,11 +11984,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12417,11 +12233,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13176,11 +12980,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13429,11 +13229,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13682,11 +13478,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -13935,11 +13727,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14188,11 +13976,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14441,11 +14225,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14690,11 +14470,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -14939,11 +14715,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15192,11 +14964,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15441,11 +15209,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15694,11 +15458,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -15947,11 +15707,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16200,11 +15956,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16453,11 +16205,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16706,11 +16454,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -16959,11 +16703,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
@@ -17212,11 +16952,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801071</t>
